--- a/data/trans_orig/P36B16-Edad-trans_orig.xlsx
+++ b/data/trans_orig/P36B16-Edad-trans_orig.xlsx
@@ -725,7 +725,7 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>2353</t>
+          <t>2695</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -735,12 +735,12 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>11615</t>
+          <t>15017</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>0,59%</t>
+          <t>0,66%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
@@ -750,7 +750,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>2,9%</t>
+          <t>3,68%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>1771</t>
+          <t>3433</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
@@ -770,12 +770,12 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>8190</t>
+          <t>10666</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>0,95%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
@@ -785,7 +785,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>2,61%</t>
+          <t>2,94%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>4124</t>
+          <t>6128</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>161</t>
+          <t>1694</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>12802</t>
+          <t>18077</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>0,58%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,02%</t>
+          <t>0,22%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>2,35%</t>
         </is>
       </c>
     </row>
@@ -838,32 +838,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>25439</t>
+          <t>23392</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>11973</t>
+          <t>10295</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>51014</t>
+          <t>43420</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>6,36%</t>
+          <t>5,74%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>2,99%</t>
+          <t>2,52%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>12,75%</t>
+          <t>10,65%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -873,32 +873,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>30687</t>
+          <t>31773</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>16851</t>
+          <t>15805</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>51357</t>
+          <t>51978</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>9,8%</t>
+          <t>8,76%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>5,38%</t>
+          <t>4,36%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>16,4%</t>
+          <t>14,34%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>56126</t>
+          <t>55166</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>34243</t>
+          <t>33964</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>84341</t>
+          <t>83681</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>7,87%</t>
+          <t>7,16%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>4,8%</t>
+          <t>4,41%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>11,83%</t>
+          <t>10,86%</t>
         </is>
       </c>
     </row>
@@ -951,32 +951,32 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>228373</t>
+          <t>227481</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>195129</t>
+          <t>196280</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>263370</t>
+          <t>257825</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>57,1%</t>
+          <t>55,78%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>48,78%</t>
+          <t>48,13%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>65,84%</t>
+          <t>63,22%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -986,32 +986,32 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>188094</t>
+          <t>204638</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>163229</t>
+          <t>176680</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>210592</t>
+          <t>229516</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>60,06%</t>
+          <t>56,45%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>52,12%</t>
+          <t>48,74%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>67,24%</t>
+          <t>63,31%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>416467</t>
+          <t>432119</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>373988</t>
+          <t>387746</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>459612</t>
+          <t>470525</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>58,4%</t>
+          <t>56,1%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>52,44%</t>
+          <t>50,34%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>64,44%</t>
+          <t>61,08%</t>
         </is>
       </c>
     </row>
@@ -1064,32 +1064,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>134049</t>
+          <t>140169</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>103399</t>
+          <t>110421</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>169162</t>
+          <t>170692</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>33,51%</t>
+          <t>34,37%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>25,85%</t>
+          <t>27,08%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>42,29%</t>
+          <t>41,86%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1099,32 +1099,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>82439</t>
+          <t>107998</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>62382</t>
+          <t>86884</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>102898</t>
+          <t>134126</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>26,32%</t>
+          <t>29,79%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>19,92%</t>
+          <t>23,97%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>32,85%</t>
+          <t>37,0%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1134,32 +1134,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>216488</t>
+          <t>248167</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>179107</t>
+          <t>212574</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>257803</t>
+          <t>292265</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>30,35%</t>
+          <t>32,22%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>25,11%</t>
+          <t>27,6%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>36,15%</t>
+          <t>37,94%</t>
         </is>
       </c>
     </row>
@@ -1177,32 +1177,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>9772</t>
+          <t>14056</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>2532</t>
+          <t>5122</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>23425</t>
+          <t>28294</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>2,44%</t>
+          <t>3,45%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>1,26%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>5,86%</t>
+          <t>6,94%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1212,32 +1212,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>10210</t>
+          <t>14669</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>3754</t>
+          <t>5859</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>22579</t>
+          <t>30400</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>3,26%</t>
+          <t>4,05%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>1,62%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>7,21%</t>
+          <t>8,39%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1247,32 +1247,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>19981</t>
+          <t>28725</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>9801</t>
+          <t>15143</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>38620</t>
+          <t>50220</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>2,8%</t>
+          <t>3,73%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>1,37%</t>
+          <t>1,97%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>5,42%</t>
+          <t>6,52%</t>
         </is>
       </c>
     </row>
@@ -1290,17 +1290,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>399987</t>
+          <t>407793</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>399987</t>
+          <t>407793</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>399987</t>
+          <t>407793</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1325,17 +1325,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>313200</t>
+          <t>362512</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>313200</t>
+          <t>362512</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>313200</t>
+          <t>362512</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1360,17 +1360,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>713187</t>
+          <t>770305</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>713187</t>
+          <t>770305</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>713187</t>
+          <t>770305</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1407,32 +1407,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>1993</t>
+          <t>5695</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>166</t>
+          <t>1474</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>9789</t>
+          <t>16836</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>0,47%</t>
+          <t>1,19%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,04%</t>
+          <t>0,31%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>2,31%</t>
+          <t>3,53%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1442,32 +1442,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>5199</t>
+          <t>5278</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>1433</t>
+          <t>1733</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>14307</t>
+          <t>13941</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>1,06%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,28%</t>
+          <t>0,35%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>2,81%</t>
+          <t>2,79%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1477,32 +1477,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>7192</t>
+          <t>10973</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>2708</t>
+          <t>5061</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>16914</t>
+          <t>21954</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>1,12%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,29%</t>
+          <t>0,52%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,81%</t>
+          <t>2,25%</t>
         </is>
       </c>
     </row>
@@ -1520,32 +1520,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>26823</t>
+          <t>33066</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>16209</t>
+          <t>19783</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>41807</t>
+          <t>48680</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>6,33%</t>
+          <t>6,93%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>3,83%</t>
+          <t>4,15%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>9,87%</t>
+          <t>10,21%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1555,32 +1555,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>32138</t>
+          <t>38031</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>19251</t>
+          <t>26889</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>47089</t>
+          <t>54373</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>6,31%</t>
+          <t>7,62%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>3,78%</t>
+          <t>5,39%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>9,24%</t>
+          <t>10,89%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1590,32 +1590,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>58961</t>
+          <t>71097</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>42136</t>
+          <t>53327</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>80816</t>
+          <t>92744</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>6,32%</t>
+          <t>7,28%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>4,51%</t>
+          <t>5,46%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>8,66%</t>
+          <t>9,5%</t>
         </is>
       </c>
     </row>
@@ -1633,32 +1633,32 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>251667</t>
+          <t>272043</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>226521</t>
+          <t>243373</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>274965</t>
+          <t>303885</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>59,42%</t>
+          <t>57,05%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>53,48%</t>
+          <t>51,03%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>64,92%</t>
+          <t>63,72%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1668,32 +1668,32 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>272745</t>
+          <t>299028</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>163829</t>
+          <t>275772</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>323725</t>
+          <t>319203</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>53,51%</t>
+          <t>59,89%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>32,14%</t>
+          <t>55,23%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>63,51%</t>
+          <t>63,93%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1703,32 +1703,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>524412</t>
+          <t>571072</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>402204</t>
+          <t>533053</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>578441</t>
+          <t>607582</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>56,19%</t>
+          <t>58,5%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>43,1%</t>
+          <t>54,6%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>61,98%</t>
+          <t>62,24%</t>
         </is>
       </c>
     </row>
@@ -1746,32 +1746,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>130977</t>
+          <t>151702</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>109669</t>
+          <t>126025</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>156881</t>
+          <t>179416</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>30,92%</t>
+          <t>31,81%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>25,89%</t>
+          <t>26,43%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>37,04%</t>
+          <t>37,62%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1781,32 +1781,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>195145</t>
+          <t>150756</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>139297</t>
+          <t>131261</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>318349</t>
+          <t>173757</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>38,28%</t>
+          <t>30,19%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>27,33%</t>
+          <t>26,29%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>62,46%</t>
+          <t>34,8%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1816,32 +1816,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>326122</t>
+          <t>302458</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>265939</t>
+          <t>267657</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>467864</t>
+          <t>339616</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>34,94%</t>
+          <t>30,98%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>28,5%</t>
+          <t>27,42%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>50,13%</t>
+          <t>34,79%</t>
         </is>
       </c>
     </row>
@@ -1859,32 +1859,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>12086</t>
+          <t>14384</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>5637</t>
+          <t>6829</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>25768</t>
+          <t>30105</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>2,85%</t>
+          <t>3,02%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>1,33%</t>
+          <t>1,43%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>6,08%</t>
+          <t>6,31%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1894,67 +1894,67 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>4490</t>
+          <t>6231</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>1444</t>
+          <t>2172</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>10774</t>
+          <t>12962</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>0,88%</t>
+          <t>1,25%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>0,28%</t>
+          <t>0,43%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
+          <t>2,6%</t>
+        </is>
+      </c>
+      <c r="Q14" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="R14" s="2" t="inlineStr">
+        <is>
+          <t>20616</t>
+        </is>
+      </c>
+      <c r="S14" s="2" t="inlineStr">
+        <is>
+          <t>11865</t>
+        </is>
+      </c>
+      <c r="T14" s="2" t="inlineStr">
+        <is>
+          <t>38318</t>
+        </is>
+      </c>
+      <c r="U14" s="2" t="inlineStr">
+        <is>
           <t>2,11%</t>
         </is>
       </c>
-      <c r="Q14" s="2" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="R14" s="2" t="inlineStr">
-        <is>
-          <t>16576</t>
-        </is>
-      </c>
-      <c r="S14" s="2" t="inlineStr">
-        <is>
-          <t>9158</t>
-        </is>
-      </c>
-      <c r="T14" s="2" t="inlineStr">
-        <is>
-          <t>30761</t>
-        </is>
-      </c>
-      <c r="U14" s="2" t="inlineStr">
-        <is>
-          <t>1,78%</t>
-        </is>
-      </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>0,98%</t>
+          <t>1,22%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>3,3%</t>
+          <t>3,93%</t>
         </is>
       </c>
     </row>
@@ -1972,17 +1972,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>423547</t>
+          <t>476890</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>423547</t>
+          <t>476890</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>423547</t>
+          <t>476890</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2007,17 +2007,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>509718</t>
+          <t>499325</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>509718</t>
+          <t>499325</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>509718</t>
+          <t>499325</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2042,17 +2042,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>933265</t>
+          <t>976216</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>933265</t>
+          <t>976216</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>933265</t>
+          <t>976216</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2089,32 +2089,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>5927</t>
+          <t>6006</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1933</t>
+          <t>2282</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>12392</t>
+          <t>14039</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>1,11%</t>
+          <t>0,97%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,36%</t>
+          <t>0,37%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>2,31%</t>
+          <t>2,26%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2124,32 +2124,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>8337</t>
+          <t>8605</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>4304</t>
+          <t>4511</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>14058</t>
+          <t>15361</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>1,54%</t>
+          <t>1,39%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,79%</t>
+          <t>0,73%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>2,47%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2159,32 +2159,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>14264</t>
+          <t>14611</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>7902</t>
+          <t>8769</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>22607</t>
+          <t>24145</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>1,18%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,71%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>1,94%</t>
         </is>
       </c>
     </row>
@@ -2202,32 +2202,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>37816</t>
+          <t>41215</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>27295</t>
+          <t>28418</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>52637</t>
+          <t>56315</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>7,05%</t>
+          <t>6,64%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>5,09%</t>
+          <t>4,58%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>9,81%</t>
+          <t>9,07%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2237,32 +2237,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>42192</t>
+          <t>47384</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>32253</t>
+          <t>36450</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>54337</t>
+          <t>59262</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>7,79%</t>
+          <t>7,63%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>5,96%</t>
+          <t>5,87%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>10,03%</t>
+          <t>9,54%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2272,32 +2272,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>80008</t>
+          <t>88598</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>63818</t>
+          <t>71617</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>96318</t>
+          <t>107222</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>7,42%</t>
+          <t>7,13%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>5,92%</t>
+          <t>5,77%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>8,94%</t>
+          <t>8,63%</t>
         </is>
       </c>
     </row>
@@ -2315,32 +2315,32 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>313956</t>
+          <t>363187</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>290034</t>
+          <t>336434</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>337526</t>
+          <t>390952</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>58,54%</t>
+          <t>58,5%</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>54,08%</t>
+          <t>54,19%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>62,93%</t>
+          <t>62,97%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2350,32 +2350,32 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>323781</t>
+          <t>362663</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>304936</t>
+          <t>342368</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>342319</t>
+          <t>384771</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>59,78%</t>
+          <t>58,38%</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>56,3%</t>
+          <t>55,11%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>63,2%</t>
+          <t>61,94%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2385,32 +2385,32 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>637737</t>
+          <t>725851</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>605091</t>
+          <t>692938</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>666454</t>
+          <t>759180</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t>59,16%</t>
+          <t>58,44%</t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>56,13%</t>
+          <t>55,79%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>61,83%</t>
+          <t>61,12%</t>
         </is>
       </c>
     </row>
@@ -2428,32 +2428,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>171788</t>
+          <t>201718</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>149696</t>
+          <t>178509</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>195691</t>
+          <t>229955</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>32,03%</t>
+          <t>32,49%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>27,91%</t>
+          <t>28,75%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>36,49%</t>
+          <t>37,04%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2463,32 +2463,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>159572</t>
+          <t>190208</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>144028</t>
+          <t>171305</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>178075</t>
+          <t>210396</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>29,46%</t>
+          <t>30,62%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>26,59%</t>
+          <t>27,57%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>32,88%</t>
+          <t>33,87%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2498,32 +2498,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>331359</t>
+          <t>391926</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>304630</t>
+          <t>361694</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>359465</t>
+          <t>424817</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>30,74%</t>
+          <t>31,55%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>28,26%</t>
+          <t>29,12%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>33,35%</t>
+          <t>34,2%</t>
         </is>
       </c>
     </row>
@@ -2541,32 +2541,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>6851</t>
+          <t>8711</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>2826</t>
+          <t>4016</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>14065</t>
+          <t>16375</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>1,28%</t>
+          <t>1,4%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>0,53%</t>
+          <t>0,65%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>2,62%</t>
+          <t>2,64%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2576,32 +2576,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>7727</t>
+          <t>12382</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>4307</t>
+          <t>7728</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>12826</t>
+          <t>18804</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>1,43%</t>
+          <t>1,99%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>1,24%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>2,37%</t>
+          <t>3,03%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2611,32 +2611,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>14578</t>
+          <t>21093</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>9135</t>
+          <t>14131</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>23257</t>
+          <t>30634</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>1,35%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>0,85%</t>
+          <t>1,14%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>2,16%</t>
+          <t>2,47%</t>
         </is>
       </c>
     </row>
@@ -2654,17 +2654,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>536338</t>
+          <t>620837</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>536338</t>
+          <t>620837</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>536338</t>
+          <t>620837</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2689,17 +2689,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>541608</t>
+          <t>621241</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>541608</t>
+          <t>621241</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>541608</t>
+          <t>621241</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2724,17 +2724,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>1077946</t>
+          <t>1242078</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>1077946</t>
+          <t>1242078</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>1077946</t>
+          <t>1242078</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2771,32 +2771,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>6596</t>
+          <t>6529</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>1733</t>
+          <t>2533</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>15319</t>
+          <t>14195</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>0,74%</t>
+          <t>0,93%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0,2%</t>
+          <t>0,36%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>1,73%</t>
+          <t>2,03%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2806,32 +2806,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>7480</t>
+          <t>8384</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>4036</t>
+          <t>4336</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>13006</t>
+          <t>14032</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>1,05%</t>
+          <t>1,14%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>0,59%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>1,83%</t>
+          <t>1,91%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2841,32 +2841,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>14076</t>
+          <t>14913</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>7443</t>
+          <t>9103</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>23670</t>
+          <t>22776</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>0,88%</t>
+          <t>1,04%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>0,47%</t>
+          <t>0,63%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>1,48%</t>
+          <t>1,58%</t>
         </is>
       </c>
     </row>
@@ -2884,32 +2884,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>53618</t>
+          <t>60061</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>23348</t>
+          <t>46282</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>80673</t>
+          <t>76856</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>6,04%</t>
+          <t>8,57%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>2,63%</t>
+          <t>6,61%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>9,09%</t>
+          <t>10,97%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2919,32 +2919,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>63842</t>
+          <t>62891</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>49165</t>
+          <t>51634</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>80718</t>
+          <t>74469</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>8,96%</t>
+          <t>8,54%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>6,9%</t>
+          <t>7,01%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>11,33%</t>
+          <t>10,11%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2954,32 +2954,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>117460</t>
+          <t>122952</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>71109</t>
+          <t>104680</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>149822</t>
+          <t>145360</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>7,34%</t>
+          <t>8,56%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>4,44%</t>
+          <t>7,28%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>9,36%</t>
+          <t>10,11%</t>
         </is>
       </c>
     </row>
@@ -2997,32 +2997,32 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>389725</t>
+          <t>420927</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>167198</t>
+          <t>391762</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>552035</t>
+          <t>447307</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>43,9%</t>
+          <t>60,08%</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>18,83%</t>
+          <t>55,92%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>62,18%</t>
+          <t>63,84%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3032,32 +3032,32 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>438766</t>
+          <t>437449</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>415081</t>
+          <t>415798</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>480538</t>
+          <t>459445</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>61,58%</t>
+          <t>59,4%</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>58,26%</t>
+          <t>56,46%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>67,44%</t>
+          <t>62,38%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3067,32 +3067,32 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>828492</t>
+          <t>858376</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>531484</t>
+          <t>825995</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>996260</t>
+          <t>895975</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
         <is>
-          <t>51,77%</t>
+          <t>59,73%</t>
         </is>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>33,21%</t>
+          <t>57,48%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>62,26%</t>
+          <t>62,35%</t>
         </is>
       </c>
     </row>
@@ -3110,32 +3110,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>178488</t>
+          <t>196662</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>72009</t>
+          <t>175030</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>256048</t>
+          <t>228032</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>20,1%</t>
+          <t>28,07%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>8,11%</t>
+          <t>24,98%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>28,84%</t>
+          <t>32,55%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3145,32 +3145,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>190995</t>
+          <t>215222</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>159011</t>
+          <t>194313</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>211211</t>
+          <t>236896</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>26,81%</t>
+          <t>29,22%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>22,32%</t>
+          <t>26,38%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>29,64%</t>
+          <t>32,17%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3180,32 +3180,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>369483</t>
+          <t>411884</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>238127</t>
+          <t>380322</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>452097</t>
+          <t>442487</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>23,09%</t>
+          <t>28,66%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>14,88%</t>
+          <t>26,46%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>28,25%</t>
+          <t>30,79%</t>
         </is>
       </c>
     </row>
@@ -3223,32 +3223,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>259360</t>
+          <t>16439</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>17196</t>
+          <t>9963</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>626837</t>
+          <t>26120</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>29,21%</t>
+          <t>2,35%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>1,94%</t>
+          <t>1,42%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>70,61%</t>
+          <t>3,73%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3258,32 +3258,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>11414</t>
+          <t>12548</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>6426</t>
+          <t>7999</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>16897</t>
+          <t>18601</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>1,09%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>2,37%</t>
+          <t>2,53%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3293,32 +3293,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>270774</t>
+          <t>28987</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>27620</t>
+          <t>20472</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>728777</t>
+          <t>40121</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>16,92%</t>
+          <t>2,02%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>1,73%</t>
+          <t>1,42%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>45,54%</t>
+          <t>2,79%</t>
         </is>
       </c>
     </row>
@@ -3336,17 +3336,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>887786</t>
+          <t>700617</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>887786</t>
+          <t>700617</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>887786</t>
+          <t>700617</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3371,17 +3371,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>712498</t>
+          <t>736495</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>712498</t>
+          <t>736495</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>712498</t>
+          <t>736495</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3406,17 +3406,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>1600285</t>
+          <t>1437112</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>1600285</t>
+          <t>1437112</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>1600285</t>
+          <t>1437112</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3453,32 +3453,32 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>4577</t>
+          <t>5393</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>1628</t>
+          <t>2022</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>9004</t>
+          <t>11098</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>0,82%</t>
+          <t>0,89%</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>0,29%</t>
+          <t>0,33%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>1,82%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3488,32 +3488,32 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>5827</t>
+          <t>7954</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>2871</t>
+          <t>4387</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>10121</t>
+          <t>13152</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>1,07%</t>
+          <t>1,31%</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>0,53%</t>
+          <t>0,72%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>1,85%</t>
+          <t>2,16%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3523,32 +3523,32 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>10404</t>
+          <t>13347</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>6345</t>
+          <t>7899</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>17020</t>
+          <t>20354</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>0,65%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>1,54%</t>
+          <t>1,67%</t>
         </is>
       </c>
     </row>
@@ -3566,32 +3566,32 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>54343</t>
+          <t>58559</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>42539</t>
+          <t>45945</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>68527</t>
+          <t>73812</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>9,68%</t>
+          <t>9,61%</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>7,58%</t>
+          <t>7,54%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>12,21%</t>
+          <t>12,11%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3601,32 +3601,32 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>61551</t>
+          <t>69974</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>51725</t>
+          <t>58701</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>73119</t>
+          <t>82312</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>11,26%</t>
+          <t>11,51%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>9,46%</t>
+          <t>9,66%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>13,37%</t>
+          <t>13,55%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3636,32 +3636,32 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>115893</t>
+          <t>128532</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>98755</t>
+          <t>109184</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>134455</t>
+          <t>147522</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>10,46%</t>
+          <t>10,56%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>8,91%</t>
+          <t>8,97%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>12,13%</t>
+          <t>12,12%</t>
         </is>
       </c>
     </row>
@@ -3679,32 +3679,32 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>331841</t>
+          <t>354667</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>309900</t>
+          <t>332273</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>354633</t>
+          <t>378488</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>59,13%</t>
+          <t>58,2%</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>55,22%</t>
+          <t>54,53%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>63,19%</t>
+          <t>62,11%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3714,32 +3714,32 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>336572</t>
+          <t>368499</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>319131</t>
+          <t>350965</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>352977</t>
+          <t>387645</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>61,56%</t>
+          <t>60,64%</t>
         </is>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>58,37%</t>
+          <t>57,75%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>64,56%</t>
+          <t>63,79%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3749,32 +3749,32 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>668413</t>
+          <t>723166</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>641207</t>
+          <t>693298</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>695209</t>
+          <t>754242</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
         <is>
-          <t>60,33%</t>
+          <t>59,42%</t>
         </is>
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>57,87%</t>
+          <t>56,97%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>62,74%</t>
+          <t>61,97%</t>
         </is>
       </c>
     </row>
@@ -3792,32 +3792,32 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>156493</t>
+          <t>175016</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>137626</t>
+          <t>153752</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>177512</t>
+          <t>196929</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>27,88%</t>
+          <t>28,72%</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>24,52%</t>
+          <t>25,23%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>31,63%</t>
+          <t>32,32%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3827,32 +3827,32 @@
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>135752</t>
+          <t>153002</t>
         </is>
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>120653</t>
+          <t>136412</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>150823</t>
+          <t>168114</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
-          <t>24,83%</t>
+          <t>25,18%</t>
         </is>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>22,07%</t>
+          <t>22,45%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>27,58%</t>
+          <t>27,66%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3862,32 +3862,32 @@
       </c>
       <c r="R31" s="2" t="inlineStr">
         <is>
-          <t>292245</t>
+          <t>328018</t>
         </is>
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>266561</t>
+          <t>302758</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>316924</t>
+          <t>356597</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
         <is>
-          <t>26,38%</t>
+          <t>26,95%</t>
         </is>
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>24,06%</t>
+          <t>24,88%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>28,6%</t>
+          <t>29,3%</t>
         </is>
       </c>
     </row>
@@ -3905,32 +3905,32 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>13980</t>
+          <t>15711</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>8411</t>
+          <t>9401</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>22772</t>
+          <t>24812</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>2,49%</t>
+          <t>2,58%</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>1,54%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>4,06%</t>
+          <t>4,07%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3940,22 +3940,22 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>7061</t>
+          <t>8252</t>
         </is>
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>3753</t>
+          <t>4182</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>11824</t>
+          <t>13715</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
-          <t>1,29%</t>
+          <t>1,36%</t>
         </is>
       </c>
       <c r="O32" s="2" t="inlineStr">
@@ -3965,7 +3965,7 @@
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>2,16%</t>
+          <t>2,26%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3975,32 +3975,32 @@
       </c>
       <c r="R32" s="2" t="inlineStr">
         <is>
-          <t>21041</t>
+          <t>23964</t>
         </is>
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>14084</t>
+          <t>16563</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>29800</t>
+          <t>34133</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>1,97%</t>
         </is>
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>1,36%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>2,69%</t>
+          <t>2,8%</t>
         </is>
       </c>
     </row>
@@ -4018,17 +4018,17 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>561234</t>
+          <t>609346</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>561234</t>
+          <t>609346</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>561234</t>
+          <t>609346</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -4053,17 +4053,17 @@
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>546762</t>
+          <t>607680</t>
         </is>
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>546762</t>
+          <t>607680</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>546762</t>
+          <t>607680</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -4088,17 +4088,17 @@
       </c>
       <c r="R33" s="2" t="inlineStr">
         <is>
-          <t>1107995</t>
+          <t>1217027</t>
         </is>
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>1107995</t>
+          <t>1217027</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>1107995</t>
+          <t>1217027</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -4135,32 +4135,32 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>2879</t>
+          <t>2803</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>1125</t>
+          <t>1083</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>6585</t>
+          <t>6233</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>0,69%</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>0,31%</t>
+          <t>0,27%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>1,79%</t>
+          <t>1,53%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4170,32 +4170,32 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>4472</t>
+          <t>5338</t>
         </is>
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>976</t>
+          <t>2376</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>9005</t>
+          <t>9684</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
-          <t>0,74%</t>
+          <t>1,22%</t>
         </is>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>0,16%</t>
+          <t>0,54%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>1,48%</t>
+          <t>2,21%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4205,32 +4205,32 @@
       </c>
       <c r="R34" s="2" t="inlineStr">
         <is>
-          <t>7351</t>
+          <t>8141</t>
         </is>
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>3248</t>
+          <t>4558</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>12511</t>
+          <t>13073</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
         <is>
-          <t>0,75%</t>
+          <t>0,96%</t>
         </is>
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>0,33%</t>
+          <t>0,54%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>1,28%</t>
+          <t>1,55%</t>
         </is>
       </c>
     </row>
@@ -4248,32 +4248,32 @@
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>40323</t>
+          <t>43340</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>31611</t>
+          <t>34204</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>51321</t>
+          <t>55550</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>10,95%</t>
+          <t>10,65%</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>8,59%</t>
+          <t>8,4%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>13,94%</t>
+          <t>13,65%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -4283,32 +4283,32 @@
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>62369</t>
+          <t>65127</t>
         </is>
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>22955</t>
+          <t>54972</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>98746</t>
+          <t>75275</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
         <is>
-          <t>10,28%</t>
+          <t>14,89%</t>
         </is>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>3,78%</t>
+          <t>12,57%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>16,28%</t>
+          <t>17,21%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4318,32 +4318,32 @@
       </c>
       <c r="R35" s="2" t="inlineStr">
         <is>
-          <t>102692</t>
+          <t>108467</t>
         </is>
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>51052</t>
+          <t>95179</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>135766</t>
+          <t>124149</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
         <is>
-          <t>10,53%</t>
+          <t>12,84%</t>
         </is>
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>5,24%</t>
+          <t>11,27%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>13,93%</t>
+          <t>14,7%</t>
         </is>
       </c>
     </row>
@@ -4361,32 +4361,32 @@
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>222909</t>
+          <t>242668</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>207658</t>
+          <t>225366</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>235531</t>
+          <t>260035</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>60,55%</t>
+          <t>59,61%</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>56,4%</t>
+          <t>55,36%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>63,97%</t>
+          <t>63,88%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4396,32 +4396,32 @@
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>220959</t>
+          <t>238721</t>
         </is>
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>91793</t>
+          <t>224823</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>340650</t>
+          <t>254172</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
-          <t>36,42%</t>
+          <t>54,57%</t>
         </is>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>15,13%</t>
+          <t>51,39%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>56,15%</t>
+          <t>58,1%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4431,32 +4431,32 @@
       </c>
       <c r="R36" s="2" t="inlineStr">
         <is>
-          <t>443868</t>
+          <t>481389</t>
         </is>
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>211946</t>
+          <t>458010</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>570924</t>
+          <t>503634</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
         <is>
-          <t>45,53%</t>
+          <t>57,0%</t>
         </is>
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>21,74%</t>
+          <t>54,23%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>58,57%</t>
+          <t>59,63%</t>
         </is>
       </c>
     </row>
@@ -4474,32 +4474,32 @@
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>97639</t>
+          <t>112367</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>85100</t>
+          <t>98065</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>111743</t>
+          <t>127363</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>26,52%</t>
+          <t>27,6%</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>23,11%</t>
+          <t>24,09%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>30,35%</t>
+          <t>31,29%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -4509,32 +4509,32 @@
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>313816</t>
+          <t>122097</t>
         </is>
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>158772</t>
+          <t>109123</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>484633</t>
+          <t>137346</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
         <is>
-          <t>51,73%</t>
+          <t>27,91%</t>
         </is>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>26,17%</t>
+          <t>24,95%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>79,88%</t>
+          <t>31,4%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4544,32 +4544,32 @@
       </c>
       <c r="R37" s="2" t="inlineStr">
         <is>
-          <t>411455</t>
+          <t>234464</t>
         </is>
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>253516</t>
+          <t>214168</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>698587</t>
+          <t>253983</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
         <is>
-          <t>42,21%</t>
+          <t>27,76%</t>
         </is>
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>26,01%</t>
+          <t>25,36%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>71,66%</t>
+          <t>30,07%</t>
         </is>
       </c>
     </row>
@@ -4587,32 +4587,32 @@
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>4415</t>
+          <t>5900</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>1907</t>
+          <t>2636</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>9243</t>
+          <t>11053</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>1,45%</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>0,52%</t>
+          <t>0,65%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>2,51%</t>
+          <t>2,72%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -4622,32 +4622,32 @@
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>5065</t>
+          <t>6171</t>
         </is>
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>1112</t>
+          <t>3057</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>10220</t>
+          <t>10853</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>1,41%</t>
         </is>
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>0,18%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>1,68%</t>
+          <t>2,48%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -4657,32 +4657,32 @@
       </c>
       <c r="R38" s="2" t="inlineStr">
         <is>
-          <t>9480</t>
+          <t>12071</t>
         </is>
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>4025</t>
+          <t>7422</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>15452</t>
+          <t>18215</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>1,43%</t>
         </is>
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>0,88%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>1,59%</t>
+          <t>2,16%</t>
         </is>
       </c>
     </row>
@@ -4700,17 +4700,17 @@
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>368165</t>
+          <t>407080</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>368165</t>
+          <t>407080</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>368165</t>
+          <t>407080</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
@@ -4735,17 +4735,17 @@
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>606682</t>
+          <t>437454</t>
         </is>
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>606682</t>
+          <t>437454</t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>606682</t>
+          <t>437454</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
@@ -4770,17 +4770,17 @@
       </c>
       <c r="R39" s="2" t="inlineStr">
         <is>
-          <t>974847</t>
+          <t>844533</t>
         </is>
       </c>
       <c r="S39" s="2" t="inlineStr">
         <is>
-          <t>974847</t>
+          <t>844533</t>
         </is>
       </c>
       <c r="T39" s="2" t="inlineStr">
         <is>
-          <t>974847</t>
+          <t>844533</t>
         </is>
       </c>
       <c r="U39" s="2" t="inlineStr">
@@ -4817,32 +4817,32 @@
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>3772</t>
+          <t>3972</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>1279</t>
+          <t>1708</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>7890</t>
+          <t>9167</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>1,33%</t>
+          <t>1,28%</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>0,45%</t>
+          <t>0,55%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>2,79%</t>
+          <t>2,96%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -4852,22 +4852,22 @@
       </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
-          <t>3624</t>
+          <t>4045</t>
         </is>
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>1558</t>
+          <t>1729</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>7406</t>
+          <t>7538</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
         <is>
-          <t>0,85%</t>
+          <t>0,87%</t>
         </is>
       </c>
       <c r="O40" s="2" t="inlineStr">
@@ -4877,7 +4877,7 @@
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>1,74%</t>
+          <t>1,62%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -4887,32 +4887,32 @@
       </c>
       <c r="R40" s="2" t="inlineStr">
         <is>
-          <t>7396</t>
+          <t>8018</t>
         </is>
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>3952</t>
+          <t>4381</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>12826</t>
+          <t>13732</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
         <is>
-          <t>1,04%</t>
+          <t>1,03%</t>
         </is>
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>0,56%</t>
+          <t>0,57%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>1,81%</t>
+          <t>1,77%</t>
         </is>
       </c>
     </row>
@@ -4930,22 +4930,22 @@
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>26369</t>
+          <t>28845</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>20003</t>
+          <t>21940</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>34538</t>
+          <t>38465</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>9,33%</t>
+          <t>9,3%</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
@@ -4955,7 +4955,7 @@
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>12,21%</t>
+          <t>12,4%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -4965,32 +4965,32 @@
       </c>
       <c r="K41" s="2" t="inlineStr">
         <is>
-          <t>63720</t>
+          <t>68664</t>
         </is>
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>53200</t>
+          <t>59088</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>74026</t>
+          <t>79923</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
         <is>
-          <t>14,96%</t>
+          <t>14,78%</t>
         </is>
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>12,49%</t>
+          <t>12,72%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>17,38%</t>
+          <t>17,2%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -5000,32 +5000,32 @@
       </c>
       <c r="R41" s="2" t="inlineStr">
         <is>
-          <t>90088</t>
+          <t>97509</t>
         </is>
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>77973</t>
+          <t>84305</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>103296</t>
+          <t>111316</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
         <is>
-          <t>12,71%</t>
+          <t>12,58%</t>
         </is>
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>11,0%</t>
+          <t>10,88%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>14,58%</t>
+          <t>14,37%</t>
         </is>
       </c>
     </row>
@@ -5043,32 +5043,32 @@
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>170083</t>
+          <t>181758</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>155417</t>
+          <t>166390</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>182050</t>
+          <t>196592</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>60,15%</t>
+          <t>58,59%</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>54,96%</t>
+          <t>53,64%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>64,38%</t>
+          <t>63,38%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -5078,32 +5078,32 @@
       </c>
       <c r="K42" s="2" t="inlineStr">
         <is>
-          <t>232741</t>
+          <t>248940</t>
         </is>
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>218846</t>
+          <t>233364</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>247555</t>
+          <t>263770</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
         <is>
-          <t>54,66%</t>
+          <t>53,58%</t>
         </is>
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>51,39%</t>
+          <t>50,23%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>58,13%</t>
+          <t>56,77%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -5113,32 +5113,32 @@
       </c>
       <c r="R42" s="2" t="inlineStr">
         <is>
-          <t>402824</t>
+          <t>430699</t>
         </is>
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>383356</t>
+          <t>408082</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>422421</t>
+          <t>452303</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
         <is>
-          <t>56,85%</t>
+          <t>55,59%</t>
         </is>
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>54,1%</t>
+          <t>52,67%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>59,61%</t>
+          <t>58,38%</t>
         </is>
       </c>
     </row>
@@ -5156,32 +5156,32 @@
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>77043</t>
+          <t>89298</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>66058</t>
+          <t>75388</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>89404</t>
+          <t>103249</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>27,25%</t>
+          <t>28,79%</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>23,36%</t>
+          <t>24,3%</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>31,62%</t>
+          <t>33,28%</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
@@ -5191,32 +5191,32 @@
       </c>
       <c r="K43" s="2" t="inlineStr">
         <is>
-          <t>118288</t>
+          <t>133500</t>
         </is>
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>106159</t>
+          <t>119399</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>131893</t>
+          <t>147982</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
         <is>
-          <t>27,78%</t>
+          <t>28,73%</t>
         </is>
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>24,93%</t>
+          <t>25,7%</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>30,97%</t>
+          <t>31,85%</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -5226,32 +5226,32 @@
       </c>
       <c r="R43" s="2" t="inlineStr">
         <is>
-          <t>195331</t>
+          <t>222798</t>
         </is>
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>177375</t>
+          <t>203205</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>213802</t>
+          <t>244807</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
         <is>
-          <t>27,57%</t>
+          <t>28,76%</t>
         </is>
       </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>25,03%</t>
+          <t>26,23%</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>30,17%</t>
+          <t>31,6%</t>
         </is>
       </c>
     </row>
@@ -5269,27 +5269,27 @@
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>5492</t>
+          <t>6324</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>2674</t>
+          <t>2970</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>10857</t>
+          <t>11904</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>1,94%</t>
+          <t>2,04%</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>0,96%</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
@@ -5304,32 +5304,32 @@
       </c>
       <c r="K44" s="2" t="inlineStr">
         <is>
-          <t>7459</t>
+          <t>9459</t>
         </is>
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>4320</t>
+          <t>5627</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>12199</t>
+          <t>15165</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
         <is>
-          <t>1,75%</t>
+          <t>2,04%</t>
         </is>
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
+          <t>1,21%</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>2,86%</t>
+          <t>3,26%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -5339,32 +5339,32 @@
       </c>
       <c r="R44" s="2" t="inlineStr">
         <is>
-          <t>12951</t>
+          <t>15784</t>
         </is>
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>8172</t>
+          <t>10465</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>19295</t>
+          <t>23301</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
         <is>
-          <t>1,83%</t>
+          <t>2,04%</t>
         </is>
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>1,15%</t>
+          <t>1,35%</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>2,72%</t>
+          <t>3,01%</t>
         </is>
       </c>
     </row>
@@ -5382,17 +5382,17 @@
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>282759</t>
+          <t>310198</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>282759</t>
+          <t>310198</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>282759</t>
+          <t>310198</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
@@ -5417,17 +5417,17 @@
       </c>
       <c r="K45" s="2" t="inlineStr">
         <is>
-          <t>425831</t>
+          <t>464609</t>
         </is>
       </c>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t>425831</t>
+          <t>464609</t>
         </is>
       </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t>425831</t>
+          <t>464609</t>
         </is>
       </c>
       <c r="N45" s="2" t="inlineStr">
@@ -5452,17 +5452,17 @@
       </c>
       <c r="R45" s="2" t="inlineStr">
         <is>
-          <t>708590</t>
+          <t>774807</t>
         </is>
       </c>
       <c r="S45" s="2" t="inlineStr">
         <is>
-          <t>708590</t>
+          <t>774807</t>
         </is>
       </c>
       <c r="T45" s="2" t="inlineStr">
         <is>
-          <t>708590</t>
+          <t>774807</t>
         </is>
       </c>
       <c r="U45" s="2" t="inlineStr">
@@ -5499,32 +5499,32 @@
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>28097</t>
+          <t>33094</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>17911</t>
+          <t>22691</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>41885</t>
+          <t>49151</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>0,81%</t>
+          <t>0,94%</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>0,52%</t>
+          <t>0,64%</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>1,21%</t>
+          <t>1,39%</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
@@ -5534,32 +5534,32 @@
       </c>
       <c r="K46" s="2" t="inlineStr">
         <is>
-          <t>36710</t>
+          <t>43037</t>
         </is>
       </c>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>26285</t>
+          <t>32958</t>
         </is>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>50782</t>
+          <t>57572</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>1,15%</t>
         </is>
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>0,88%</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>1,39%</t>
+          <t>1,54%</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -5569,32 +5569,32 @@
       </c>
       <c r="R46" s="2" t="inlineStr">
         <is>
-          <t>64807</t>
+          <t>76132</t>
         </is>
       </c>
       <c r="S46" s="2" t="inlineStr">
         <is>
-          <t>49422</t>
+          <t>59512</t>
         </is>
       </c>
       <c r="T46" s="2" t="inlineStr">
         <is>
-          <t>82907</t>
+          <t>95583</t>
         </is>
       </c>
       <c r="U46" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>1,05%</t>
         </is>
       </c>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>0,82%</t>
         </is>
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>1,32%</t>
         </is>
       </c>
     </row>
@@ -5612,32 +5612,32 @@
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>264731</t>
+          <t>288477</t>
         </is>
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>209287</t>
+          <t>253624</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>305810</t>
+          <t>328688</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t>7,65%</t>
+          <t>8,17%</t>
         </is>
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>6,05%</t>
+          <t>7,18%</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>8,84%</t>
+          <t>9,3%</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
@@ -5647,32 +5647,32 @@
       </c>
       <c r="K47" s="2" t="inlineStr">
         <is>
-          <t>356498</t>
+          <t>383844</t>
         </is>
       </c>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>288961</t>
+          <t>353292</t>
         </is>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>400882</t>
+          <t>416772</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
         <is>
-          <t>9,75%</t>
+          <t>10,29%</t>
         </is>
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>7,9%</t>
+          <t>9,47%</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>10,96%</t>
+          <t>11,18%</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
@@ -5682,32 +5682,32 @@
       </c>
       <c r="R47" s="2" t="inlineStr">
         <is>
-          <t>621230</t>
+          <t>672321</t>
         </is>
       </c>
       <c r="S47" s="2" t="inlineStr">
         <is>
-          <t>537359</t>
+          <t>626851</t>
         </is>
       </c>
       <c r="T47" s="2" t="inlineStr">
         <is>
-          <t>688465</t>
+          <t>725902</t>
         </is>
       </c>
       <c r="U47" s="2" t="inlineStr">
         <is>
-          <t>8,73%</t>
+          <t>9,26%</t>
         </is>
       </c>
       <c r="V47" s="2" t="inlineStr">
         <is>
-          <t>7,55%</t>
+          <t>8,63%</t>
         </is>
       </c>
       <c r="W47" s="2" t="inlineStr">
         <is>
-          <t>9,67%</t>
+          <t>10,0%</t>
         </is>
       </c>
     </row>
@@ -5725,32 +5725,32 @@
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>1908556</t>
+          <t>2062732</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>1478008</t>
+          <t>1999908</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>2075082</t>
+          <t>2130598</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t>55,16%</t>
+          <t>58,39%</t>
         </is>
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>42,72%</t>
+          <t>56,61%</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>59,98%</t>
+          <t>60,31%</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr">
@@ -5760,67 +5760,67 @@
       </c>
       <c r="K48" s="2" t="inlineStr">
         <is>
-          <t>2013657</t>
+          <t>2159939</t>
         </is>
       </c>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>1622787</t>
+          <t>2106401</t>
         </is>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>2165061</t>
+          <t>2217038</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
         <is>
-          <t>55,07%</t>
+          <t>57,92%</t>
         </is>
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>44,38%</t>
+          <t>56,48%</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
+          <t>59,45%</t>
+        </is>
+      </c>
+      <c r="Q48" s="2" t="inlineStr">
+        <is>
+          <t>5186</t>
+        </is>
+      </c>
+      <c r="R48" s="2" t="inlineStr">
+        <is>
+          <t>4222671</t>
+        </is>
+      </c>
+      <c r="S48" s="2" t="inlineStr">
+        <is>
+          <t>4129249</t>
+        </is>
+      </c>
+      <c r="T48" s="2" t="inlineStr">
+        <is>
+          <t>4300041</t>
+        </is>
+      </c>
+      <c r="U48" s="2" t="inlineStr">
+        <is>
+          <t>58,15%</t>
+        </is>
+      </c>
+      <c r="V48" s="2" t="inlineStr">
+        <is>
+          <t>56,86%</t>
+        </is>
+      </c>
+      <c r="W48" s="2" t="inlineStr">
+        <is>
           <t>59,21%</t>
-        </is>
-      </c>
-      <c r="Q48" s="2" t="inlineStr">
-        <is>
-          <t>5186</t>
-        </is>
-      </c>
-      <c r="R48" s="2" t="inlineStr">
-        <is>
-          <t>3922213</t>
-        </is>
-      </c>
-      <c r="S48" s="2" t="inlineStr">
-        <is>
-          <t>3370567</t>
-        </is>
-      </c>
-      <c r="T48" s="2" t="inlineStr">
-        <is>
-          <t>4191834</t>
-        </is>
-      </c>
-      <c r="U48" s="2" t="inlineStr">
-        <is>
-          <t>55,12%</t>
-        </is>
-      </c>
-      <c r="V48" s="2" t="inlineStr">
-        <is>
-          <t>47,37%</t>
-        </is>
-      </c>
-      <c r="W48" s="2" t="inlineStr">
-        <is>
-          <t>58,91%</t>
         </is>
       </c>
     </row>
@@ -5838,32 +5838,32 @@
       </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
-          <t>946477</t>
+          <t>1066933</t>
         </is>
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>742508</t>
+          <t>1008272</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>1039801</t>
+          <t>1128449</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
         <is>
-          <t>27,36%</t>
+          <t>30,2%</t>
         </is>
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>21,46%</t>
+          <t>28,54%</t>
         </is>
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>30,05%</t>
+          <t>31,94%</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr">
@@ -5873,32 +5873,32 @@
       </c>
       <c r="K49" s="2" t="inlineStr">
         <is>
-          <t>1196008</t>
+          <t>1072784</t>
         </is>
       </c>
       <c r="L49" s="2" t="inlineStr">
         <is>
-          <t>1009956</t>
+          <t>1024179</t>
         </is>
       </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t>1653539</t>
+          <t>1121302</t>
         </is>
       </c>
       <c r="N49" s="2" t="inlineStr">
         <is>
-          <t>32,71%</t>
+          <t>28,77%</t>
         </is>
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>27,62%</t>
+          <t>27,46%</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
         <is>
-          <t>45,22%</t>
+          <t>30,07%</t>
         </is>
       </c>
       <c r="Q49" s="2" t="inlineStr">
@@ -5908,32 +5908,32 @@
       </c>
       <c r="R49" s="2" t="inlineStr">
         <is>
-          <t>2142484</t>
+          <t>2139717</t>
         </is>
       </c>
       <c r="S49" s="2" t="inlineStr">
         <is>
-          <t>1905098</t>
+          <t>2061876</t>
         </is>
       </c>
       <c r="T49" s="2" t="inlineStr">
         <is>
-          <t>2638603</t>
+          <t>2223976</t>
         </is>
       </c>
       <c r="U49" s="2" t="inlineStr">
         <is>
-          <t>30,11%</t>
+          <t>29,46%</t>
         </is>
       </c>
       <c r="V49" s="2" t="inlineStr">
         <is>
-          <t>26,77%</t>
+          <t>28,39%</t>
         </is>
       </c>
       <c r="W49" s="2" t="inlineStr">
         <is>
-          <t>37,08%</t>
+          <t>30,62%</t>
         </is>
       </c>
     </row>
@@ -5951,32 +5951,32 @@
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>311956</t>
+          <t>81526</t>
         </is>
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>66134</t>
+          <t>63313</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>1005545</t>
+          <t>108949</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t>9,02%</t>
+          <t>2,31%</t>
         </is>
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>1,91%</t>
+          <t>1,79%</t>
         </is>
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>29,06%</t>
+          <t>3,08%</t>
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr">
@@ -5986,32 +5986,32 @@
       </c>
       <c r="K50" s="2" t="inlineStr">
         <is>
-          <t>53426</t>
+          <t>69713</t>
         </is>
       </c>
       <c r="L50" s="2" t="inlineStr">
         <is>
-          <t>39924</t>
+          <t>56148</t>
         </is>
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>69532</t>
+          <t>88744</t>
         </is>
       </c>
       <c r="N50" s="2" t="inlineStr">
         <is>
-          <t>1,46%</t>
+          <t>1,87%</t>
         </is>
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>1,09%</t>
+          <t>1,51%</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>2,38%</t>
         </is>
       </c>
       <c r="Q50" s="2" t="inlineStr">
@@ -6021,32 +6021,32 @@
       </c>
       <c r="R50" s="2" t="inlineStr">
         <is>
-          <t>365382</t>
+          <t>151238</t>
         </is>
       </c>
       <c r="S50" s="2" t="inlineStr">
         <is>
-          <t>116360</t>
+          <t>125158</t>
         </is>
       </c>
       <c r="T50" s="2" t="inlineStr">
         <is>
-          <t>1245530</t>
+          <t>179587</t>
         </is>
       </c>
       <c r="U50" s="2" t="inlineStr">
         <is>
-          <t>5,13%</t>
+          <t>2,08%</t>
         </is>
       </c>
       <c r="V50" s="2" t="inlineStr">
         <is>
-          <t>1,64%</t>
+          <t>1,72%</t>
         </is>
       </c>
       <c r="W50" s="2" t="inlineStr">
         <is>
-          <t>17,5%</t>
+          <t>2,47%</t>
         </is>
       </c>
     </row>
@@ -6064,17 +6064,17 @@
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
-          <t>3459817</t>
+          <t>3532762</t>
         </is>
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>3459817</t>
+          <t>3532762</t>
         </is>
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
-          <t>3459817</t>
+          <t>3532762</t>
         </is>
       </c>
       <c r="G51" s="2" t="inlineStr">
@@ -6099,17 +6099,17 @@
       </c>
       <c r="K51" s="2" t="inlineStr">
         <is>
-          <t>3656299</t>
+          <t>3729317</t>
         </is>
       </c>
       <c r="L51" s="2" t="inlineStr">
         <is>
-          <t>3656299</t>
+          <t>3729317</t>
         </is>
       </c>
       <c r="M51" s="2" t="inlineStr">
         <is>
-          <t>3656299</t>
+          <t>3729317</t>
         </is>
       </c>
       <c r="N51" s="2" t="inlineStr">
@@ -6134,17 +6134,17 @@
       </c>
       <c r="R51" s="2" t="inlineStr">
         <is>
-          <t>7116116</t>
+          <t>7262079</t>
         </is>
       </c>
       <c r="S51" s="2" t="inlineStr">
         <is>
-          <t>7116116</t>
+          <t>7262079</t>
         </is>
       </c>
       <c r="T51" s="2" t="inlineStr">
         <is>
-          <t>7116116</t>
+          <t>7262079</t>
         </is>
       </c>
       <c r="U51" s="2" t="inlineStr">
